--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6569CD44-97B9-4899-806A-1B3C47230813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5432644-E076-4755-8461-1FEDB4FD6791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOJ 문제 정리" sheetId="1" r:id="rId1"/>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 11000 / 강의실배정</v>
+        <v>Silver / 2805 / 나무자르기</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1010,7 +1010,7 @@
         <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
@@ -1061,7 +1061,7 @@
         <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5432644-E076-4755-8461-1FEDB4FD6791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30523D97-4120-482F-9BB7-8C08EE314A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 2805 / 나무자르기</v>
+        <v>Gold / 1300 / k번째수</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1299,7 +1299,7 @@
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30523D97-4120-482F-9BB7-8C08EE314A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CFE068-708F-458B-BD97-D3481D0CDD46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 1300 / k번째수</v>
+        <v>Silver / 1966 / 프린터큐</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -670,7 +670,7 @@
         <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CFE068-708F-458B-BD97-D3481D0CDD46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3992E2-77EA-4E18-86B2-111CF4D5ECD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1966 / 프린터큐</v>
+        <v>Silver / 1515 / 수이어쓰기</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -789,7 +789,7 @@
         <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3992E2-77EA-4E18-86B2-111CF4D5ECD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A846E28-2DCF-4CD7-90A8-9BFC68C1171D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1515 / 수이어쓰기</v>
+        <v>Gold / 2110 / 공유기설치</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1214,7 +1214,7 @@
         <v>7</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A846E28-2DCF-4CD7-90A8-9BFC68C1171D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AEB0F92-273E-4990-AE47-11B749A551B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 2110 / 공유기설치</v>
+        <v>Bronze / 9093 / 단어 뒤집기</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -738,7 +738,7 @@
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AEB0F92-273E-4990-AE47-11B749A551B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C71A174-C7C3-4A17-A39A-7655668F1874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Bronze / 9093 / 단어 뒤집기</v>
+        <v>Silver / 1406 / 에디터</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -653,7 +653,7 @@
         <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
@@ -908,7 +908,7 @@
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C71A174-C7C3-4A17-A39A-7655668F1874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09BDD697-B5E2-46EE-8A6D-CCD160520541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1406 / 에디터</v>
+        <v>Silver / 14940 / 쉬운최단거리</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1044,7 +1044,7 @@
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09BDD697-B5E2-46EE-8A6D-CCD160520541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE676703-A278-4EDB-A13A-C93CB494B35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 14940 / 쉬운최단거리</v>
+        <v>Gold / 1715 / 카드정렬하기</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1350,7 +1350,7 @@
         <v>7</v>
       </c>
       <c r="E44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE676703-A278-4EDB-A13A-C93CB494B35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8ACE1B-8A5D-4F52-84B1-2157108A2FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 1715 / 카드정렬하기</v>
+        <v>Silver / 14940 / 쉬운최단거리</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -874,7 +874,7 @@
         <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8ACE1B-8A5D-4F52-84B1-2157108A2FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B23B66-F6BA-47AF-A920-38AE3861F219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 14940 / 쉬운최단거리</v>
+        <v>Silver / 11723 / 집합</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1163,7 +1163,7 @@
         <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B23B66-F6BA-47AF-A920-38AE3861F219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E006F63-1B4F-4EDE-B01A-460A999EA255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 11723 / 집합</v>
+        <v>Silver / 2164 / 카드2</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -755,7 +755,7 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E006F63-1B4F-4EDE-B01A-460A999EA255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4468B9-2F1B-4C76-B160-061C821B9C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 2164 / 카드2</v>
+        <v>Silver / 14940 / 쉬운최단거리</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1112,7 +1112,7 @@
         <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
@@ -1129,7 +1129,7 @@
         <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4468B9-2F1B-4C76-B160-061C821B9C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBCD1C3-5E90-47CA-A428-1553E0451510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 14940 / 쉬운최단거리</v>
+        <v>Gold / 3190 / 뱀</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1418,7 +1418,7 @@
         <v>7</v>
       </c>
       <c r="E48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBCD1C3-5E90-47CA-A428-1553E0451510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCF144D-F216-46CA-81F8-31EB8D73B29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 3190 / 뱀</v>
+        <v>Gold / 7662 / 이중우선순위큐</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1282,7 +1282,7 @@
         <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCF144D-F216-46CA-81F8-31EB8D73B29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44216C6-10ED-4601-BE6F-176BA3FE8E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 7662 / 이중우선순위큐</v>
+        <v>Silver / 7568 / 덩치</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1265,7 +1265,7 @@
         <v>7</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44216C6-10ED-4601-BE6F-176BA3FE8E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C868FC5B-9FEA-4702-A3AE-CCF64C697CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 7568 / 덩치</v>
+        <v>Silver / 2805 / 나무자르기</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1180,7 +1180,7 @@
         <v>7</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C868FC5B-9FEA-4702-A3AE-CCF64C697CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C120609C-B20D-44E5-91CD-10356B2F1F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 2805 / 나무자르기</v>
+        <v>Gold / 7662 / 이중우선순위큐</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -704,7 +704,7 @@
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C120609C-B20D-44E5-91CD-10356B2F1F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964F941B-E135-45F9-A31E-62B00D6CF201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 7662 / 이중우선순위큐</v>
+        <v>Silver / 1927 / 최소힙</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -721,7 +721,7 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964F941B-E135-45F9-A31E-62B00D6CF201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96288855-A9CF-4B19-91D1-CF3AB54FD81C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1927 / 최소힙</v>
+        <v>Silver / 13305 / 주유소</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -857,7 +857,7 @@
         <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96288855-A9CF-4B19-91D1-CF3AB54FD81C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179693D1-EEFB-42D1-9F01-6459437EA717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 13305 / 주유소</v>
+        <v>Silver / 1515 / 수이어쓰기</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1367,7 +1367,7 @@
         <v>7</v>
       </c>
       <c r="E45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179693D1-EEFB-42D1-9F01-6459437EA717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8002E8-F92D-4904-B8C8-DCDCBA17168D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1401,7 +1401,7 @@
         <v>7</v>
       </c>
       <c r="E47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8002E8-F92D-4904-B8C8-DCDCBA17168D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4147D4D-ECF7-4705-A7E5-F3A2D5DB9AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1515 / 수이어쓰기</v>
+        <v>Bronze / 1157 / 단어공부</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -976,7 +976,7 @@
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4147D4D-ECF7-4705-A7E5-F3A2D5DB9AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7127AE12-9B47-42E7-9F71-C1EA44CEF3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Bronze / 1157 / 단어공부</v>
+        <v>Silver / 1927 / 최소힙</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1248,7 +1248,7 @@
         <v>7</v>
       </c>
       <c r="E38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7127AE12-9B47-42E7-9F71-C1EA44CEF3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3753FAF1-B6C8-4EC7-BFA2-91B50647AB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1927 / 최소힙</v>
+        <v>Gold / 3190 / 뱀</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1146,7 +1146,7 @@
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3753FAF1-B6C8-4EC7-BFA2-91B50647AB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77DE9EC-D011-4010-8A5F-2ABE04495391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 3190 / 뱀</v>
+        <v>Silver / 1244 / 스위치켜끄기</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -942,7 +942,7 @@
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77DE9EC-D011-4010-8A5F-2ABE04495391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C559FD-5FDA-45DC-9306-5F10FA1DA507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1244 / 스위치켜끄기</v>
+        <v>Silver / 4659 / 비밀발음</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1027,7 +1027,7 @@
         <v>7</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C559FD-5FDA-45DC-9306-5F10FA1DA507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36B642A-2AD1-40F7-A561-C195616F9876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 4659 / 비밀발음</v>
+        <v>Silver / 1244 / 스위치켜끄기</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1316,7 +1316,7 @@
         <v>7</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36B642A-2AD1-40F7-A561-C195616F9876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561D6FB2-4075-4FE2-BB82-3D76F1BD8FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1244 / 스위치켜끄기</v>
+        <v>Silver / 20922 / 겹치는건싫엉</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1333,7 +1333,7 @@
         <v>7</v>
       </c>
       <c r="E43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561D6FB2-4075-4FE2-BB82-3D76F1BD8FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C28B5F7-090F-45D4-85F7-FF6EC0D1F67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 20922 / 겹치는건싫엉</v>
+        <v>Gold / 3190 / 뱀</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1384,7 +1384,7 @@
         <v>7</v>
       </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C28B5F7-090F-45D4-85F7-FF6EC0D1F67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DDBD25-FA11-4808-8EAF-6F46F775FC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 3190 / 뱀</v>
+        <v>Bronze / 1157 / 단어공부</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1197,7 +1197,7 @@
         <v>7</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DDBD25-FA11-4808-8EAF-6F46F775FC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91AE753F-0E48-43A4-A81A-08482EE4500E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Bronze / 1157 / 단어공부</v>
+        <v>Silver / 20922 / 겹치는건싫엉</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -636,7 +636,7 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91AE753F-0E48-43A4-A81A-08482EE4500E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8825F340-0C77-4D60-886E-3E48C9F9F401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 20922 / 겹치는건싫엉</v>
+        <v>Silver / 14940 / 쉬운최단거리</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -840,7 +840,7 @@
         <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8825F340-0C77-4D60-886E-3E48C9F9F401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB4AC56-8250-4CC4-9CD8-0F008C70EC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 14940 / 쉬운최단거리</v>
+        <v>Silver / 1244 / 스위치켜끄기</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -687,7 +687,7 @@
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
@@ -1095,7 +1095,7 @@
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB4AC56-8250-4CC4-9CD8-0F008C70EC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DEEEF1-A240-479C-A055-E7B904E4EB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1244 / 스위치켜끄기</v>
+        <v>Gold / 3190 / 뱀</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -806,7 +806,7 @@
         <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DEEEF1-A240-479C-A055-E7B904E4EB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3816EC09-2D20-4020-8546-F8BF86779544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1231,7 +1231,7 @@
         <v>7</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3816EC09-2D20-4020-8546-F8BF86779544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341C552A-A55A-41DA-A6A1-A41CC935CD98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 3190 / 뱀</v>
+        <v>Silver / 14940 / 쉬운최단거리</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -993,7 +993,7 @@
         <v>7</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341C552A-A55A-41DA-A6A1-A41CC935CD98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB803529-2354-43A6-8F8D-14E422C30C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="60">
   <si>
     <t>단계</t>
   </si>
@@ -231,6 +231,10 @@
   </si>
   <si>
     <t>O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잃어버린괄호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -590,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -619,7 +623,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 14940 / 쉬운최단거리</v>
+        <v>Gold / 3190 / 뱀</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1419,6 +1423,23 @@
       </c>
       <c r="E48" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49">
+        <v>1541</v>
+      </c>
+      <c r="C49" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB803529-2354-43A6-8F8D-14E422C30C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15517EA-4900-4843-8869-37E213D50E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="61">
   <si>
     <t>단계</t>
   </si>
@@ -235,6 +235,10 @@
   </si>
   <si>
     <t>잃어버린괄호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATM</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -594,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -623,7 +627,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 3190 / 뱀</v>
+        <v>Silver / 14940 / 쉬운최단거리</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1439,6 +1443,23 @@
         <v>7</v>
       </c>
       <c r="E49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>20</v>
+      </c>
+      <c r="B50">
+        <v>11399</v>
+      </c>
+      <c r="C50" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15517EA-4900-4843-8869-37E213D50E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4519B945-2E21-48CC-81A2-DF1FD5B0CCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="62">
   <si>
     <t>단계</t>
   </si>
@@ -239,6 +239,10 @@
   </si>
   <si>
     <t>ATM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수들의합</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -598,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -627,7 +631,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 14940 / 쉬운최단거리</v>
+        <v>Gold / 3190 / 뱀</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1460,6 +1464,23 @@
         <v>7</v>
       </c>
       <c r="E50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51">
+        <v>1789</v>
+      </c>
+      <c r="C51" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4519B945-2E21-48CC-81A2-DF1FD5B0CCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8B774A-6EC2-40A5-BF70-6E62E7611D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -631,7 +631,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 3190 / 뱀</v>
+        <v>Silver / 14940 / 쉬운최단거리</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1447,7 +1447,7 @@
         <v>7</v>
       </c>
       <c r="E49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8B774A-6EC2-40A5-BF70-6E62E7611D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A899F2C-222B-4E9D-99A3-5CEC3532669C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1464,7 +1464,7 @@
         <v>7</v>
       </c>
       <c r="E50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A899F2C-222B-4E9D-99A3-5CEC3532669C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E1C841-AFC7-4232-AF3E-C17A6ACFC4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="63">
   <si>
     <t>단계</t>
   </si>
@@ -243,6 +243,10 @@
   </si>
   <si>
     <t>수들의합</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동전0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -602,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -631,7 +635,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 14940 / 쉬운최단거리</v>
+        <v>Silver / 11047 / 동전0</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1481,6 +1485,23 @@
         <v>7</v>
       </c>
       <c r="E51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52">
+        <v>11047</v>
+      </c>
+      <c r="C52" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E1C841-AFC7-4232-AF3E-C17A6ACFC4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B48C71-73BD-427A-92DD-D825DB1E0CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="64">
   <si>
     <t>단계</t>
   </si>
@@ -247,6 +247,10 @@
   </si>
   <si>
     <t>동전0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로프</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -606,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -635,7 +639,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 11047 / 동전0</v>
+        <v>Gold / 3190 / 뱀</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1502,6 +1506,23 @@
         <v>7</v>
       </c>
       <c r="E52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>20</v>
+      </c>
+      <c r="B53">
+        <v>2217</v>
+      </c>
+      <c r="C53" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B48C71-73BD-427A-92DD-D825DB1E0CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176E3ED2-103D-41FB-81CF-6A10EA6C6F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="65">
   <si>
     <t>단계</t>
   </si>
@@ -251,6 +251,10 @@
   </si>
   <si>
     <t>로프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크로스컨트리</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -610,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1526,6 +1530,23 @@
         <v>8</v>
       </c>
     </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54">
+        <v>9017</v>
+      </c>
+      <c r="C54" t="s">
+        <v>64</v>
+      </c>
+      <c r="D54" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G1:H1"/>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176E3ED2-103D-41FB-81CF-6A10EA6C6F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC4A59B-1919-4446-B43A-222D53254239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="66">
   <si>
     <t>단계</t>
   </si>
@@ -255,6 +255,10 @@
   </si>
   <si>
     <t>크로스컨트리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -614,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -643,7 +647,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 3190 / 뱀</v>
+        <v>Silver / 1026 / 보물</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1544,6 +1548,23 @@
         <v>7</v>
       </c>
       <c r="E54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55">
+        <v>1026</v>
+      </c>
+      <c r="C55" t="s">
+        <v>65</v>
+      </c>
+      <c r="D55" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC4A59B-1919-4446-B43A-222D53254239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED7BE34-3BA1-438F-A4A0-2E4BE4C39FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="67">
   <si>
     <t>단계</t>
   </si>
@@ -259,6 +259,10 @@
   </si>
   <si>
     <t>보물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>색종이</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -618,7 +622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -647,7 +651,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1026 / 보물</v>
+        <v>Silver / 1789 / 수들의합</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1565,6 +1569,23 @@
         <v>7</v>
       </c>
       <c r="E55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56">
+        <v>2563</v>
+      </c>
+      <c r="C56" t="s">
+        <v>66</v>
+      </c>
+      <c r="D56" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED7BE34-3BA1-438F-A4A0-2E4BE4C39FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2AF339-AA50-4AA3-AB17-AE66AA7E2104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="68">
   <si>
     <t>단계</t>
   </si>
@@ -263,6 +263,10 @@
   </si>
   <si>
     <t>색종이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>블로그</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -622,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -651,7 +655,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1789 / 수들의합</v>
+        <v>Silver / 2563 / 색종이</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1586,6 +1590,23 @@
         <v>7</v>
       </c>
       <c r="E56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57">
+        <v>21921</v>
+      </c>
+      <c r="C57" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2AF339-AA50-4AA3-AB17-AE66AA7E2104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439E6AC1-EE89-4712-A4B4-957ABD6ED98A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="69">
   <si>
     <t>단계</t>
   </si>
@@ -267,6 +267,10 @@
   </si>
   <si>
     <t>블로그</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수열</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -626,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -655,7 +659,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 2563 / 색종이</v>
+        <v>Silver / 1026 / 보물</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1607,6 +1611,23 @@
         <v>7</v>
       </c>
       <c r="E57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58">
+        <v>2559</v>
+      </c>
+      <c r="C58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439E6AC1-EE89-4712-A4B4-957ABD6ED98A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA00541-52ED-477B-9D12-7B282A75C46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="70">
   <si>
     <t>단계</t>
   </si>
@@ -271,6 +271,10 @@
   </si>
   <si>
     <t>수열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿀알바</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -630,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1631,6 +1635,23 @@
         <v>8</v>
       </c>
     </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59">
+        <v>12847</v>
+      </c>
+      <c r="C59" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G1:H1"/>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA00541-52ED-477B-9D12-7B282A75C46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52508D7F-6AD3-4EB5-9937-74E6DD831796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7980" yWindow="1550" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOJ 문제 정리" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="71">
   <si>
     <t>단계</t>
   </si>
@@ -275,6 +275,10 @@
   </si>
   <si>
     <t>꿀알바</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분합</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -634,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -659,11 +663,11 @@
       <c r="H1" s="1"/>
       <c r="I1" t="str" cm="1">
         <f t="array" aca="1" ref="I1" ca="1">_xlfn.LET(
-    _xlpm.reviewRows, _xlfn._xlws.FILTER(ROW(E2:E1000), E2:E1000="X"),
+    _xlpm.reviewRows, _xlfn._xlws.FILTER(ROW(E2:E1001), E2:E1001="X"),
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1026 / 보물</v>
+        <v>Silver / 11047 / 동전0</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -855,19 +859,19 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B13">
-        <v>1021</v>
+        <v>1806</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
@@ -875,10 +879,10 @@
         <v>20</v>
       </c>
       <c r="B14">
-        <v>10431</v>
+        <v>1021</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -892,10 +896,10 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>10866</v>
+        <v>10431</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -909,10 +913,10 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>11279</v>
+        <v>10866</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -926,16 +930,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>11286</v>
+        <v>11279</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
@@ -943,16 +947,16 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>1138</v>
+        <v>11286</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
@@ -960,10 +964,10 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>1158</v>
+        <v>1138</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -977,10 +981,10 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>11723</v>
+        <v>1158</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -994,10 +998,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>11866</v>
+        <v>11723</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -1011,10 +1015,10 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>1205</v>
+        <v>11866</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -1028,10 +1032,10 @@
         <v>20</v>
       </c>
       <c r="B23">
-        <v>1244</v>
+        <v>1205</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -1045,10 +1049,10 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>1260</v>
+        <v>1244</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -1062,10 +1066,10 @@
         <v>20</v>
       </c>
       <c r="B25">
-        <v>13305</v>
+        <v>1260</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -1079,10 +1083,10 @@
         <v>20</v>
       </c>
       <c r="B26">
-        <v>1406</v>
+        <v>13305</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -1096,10 +1100,10 @@
         <v>20</v>
       </c>
       <c r="B27">
-        <v>1417</v>
+        <v>1406</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -1113,16 +1117,16 @@
         <v>20</v>
       </c>
       <c r="B28">
-        <v>14940</v>
+        <v>1417</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
@@ -1130,16 +1134,16 @@
         <v>20</v>
       </c>
       <c r="B29">
-        <v>1515</v>
+        <v>14940</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
@@ -1147,10 +1151,10 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>1654</v>
+        <v>1515</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -1164,10 +1168,10 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>17266</v>
+        <v>1654</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -1181,10 +1185,10 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>1927</v>
+        <v>17266</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -1198,10 +1202,10 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>1931</v>
+        <v>1927</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -1215,10 +1219,10 @@
         <v>20</v>
       </c>
       <c r="B34">
-        <v>1966</v>
+        <v>1931</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -1232,10 +1236,10 @@
         <v>20</v>
       </c>
       <c r="B35">
-        <v>20006</v>
+        <v>1966</v>
       </c>
       <c r="C35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -1249,10 +1253,10 @@
         <v>20</v>
       </c>
       <c r="B36">
-        <v>2075</v>
+        <v>20006</v>
       </c>
       <c r="C36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -1266,10 +1270,10 @@
         <v>20</v>
       </c>
       <c r="B37">
-        <v>20922</v>
+        <v>2075</v>
       </c>
       <c r="C37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -1283,10 +1287,10 @@
         <v>20</v>
       </c>
       <c r="B38">
-        <v>2164</v>
+        <v>20922</v>
       </c>
       <c r="C38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -1300,10 +1304,10 @@
         <v>20</v>
       </c>
       <c r="B39">
-        <v>2346</v>
+        <v>2164</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -1317,10 +1321,10 @@
         <v>20</v>
       </c>
       <c r="B40">
-        <v>2512</v>
+        <v>2346</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -1334,10 +1338,10 @@
         <v>20</v>
       </c>
       <c r="B41">
-        <v>25757</v>
+        <v>2512</v>
       </c>
       <c r="C41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -1351,10 +1355,10 @@
         <v>20</v>
       </c>
       <c r="B42">
-        <v>2805</v>
+        <v>25757</v>
       </c>
       <c r="C42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -1368,10 +1372,10 @@
         <v>20</v>
       </c>
       <c r="B43">
-        <v>4659</v>
+        <v>2805</v>
       </c>
       <c r="C43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -1385,10 +1389,10 @@
         <v>20</v>
       </c>
       <c r="B44">
-        <v>5397</v>
+        <v>4659</v>
       </c>
       <c r="C44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -1402,10 +1406,10 @@
         <v>20</v>
       </c>
       <c r="B45">
-        <v>6236</v>
+        <v>5397</v>
       </c>
       <c r="C45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -1419,10 +1423,10 @@
         <v>20</v>
       </c>
       <c r="B46">
-        <v>7568</v>
+        <v>6236</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -1436,10 +1440,10 @@
         <v>20</v>
       </c>
       <c r="B47">
-        <v>8979</v>
+        <v>7568</v>
       </c>
       <c r="C47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -1453,10 +1457,10 @@
         <v>20</v>
       </c>
       <c r="B48">
-        <v>9655</v>
+        <v>8979</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -1470,10 +1474,10 @@
         <v>20</v>
       </c>
       <c r="B49">
-        <v>1541</v>
+        <v>9655</v>
       </c>
       <c r="C49" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -1487,10 +1491,10 @@
         <v>20</v>
       </c>
       <c r="B50">
-        <v>11399</v>
+        <v>1541</v>
       </c>
       <c r="C50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -1504,16 +1508,16 @@
         <v>20</v>
       </c>
       <c r="B51">
-        <v>1789</v>
+        <v>11399</v>
       </c>
       <c r="C51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
       </c>
       <c r="E51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
@@ -1521,10 +1525,10 @@
         <v>20</v>
       </c>
       <c r="B52">
-        <v>11047</v>
+        <v>1789</v>
       </c>
       <c r="C52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -1538,10 +1542,10 @@
         <v>20</v>
       </c>
       <c r="B53">
-        <v>2217</v>
+        <v>11047</v>
       </c>
       <c r="C53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -1555,10 +1559,10 @@
         <v>20</v>
       </c>
       <c r="B54">
-        <v>9017</v>
+        <v>2217</v>
       </c>
       <c r="C54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -1572,10 +1576,10 @@
         <v>20</v>
       </c>
       <c r="B55">
-        <v>1026</v>
+        <v>9017</v>
       </c>
       <c r="C55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -1589,10 +1593,10 @@
         <v>20</v>
       </c>
       <c r="B56">
-        <v>2563</v>
+        <v>1026</v>
       </c>
       <c r="C56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -1606,10 +1610,10 @@
         <v>20</v>
       </c>
       <c r="B57">
-        <v>21921</v>
+        <v>2563</v>
       </c>
       <c r="C57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -1623,10 +1627,10 @@
         <v>20</v>
       </c>
       <c r="B58">
-        <v>2559</v>
+        <v>21921</v>
       </c>
       <c r="C58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -1640,15 +1644,32 @@
         <v>20</v>
       </c>
       <c r="B59">
+        <v>2559</v>
+      </c>
+      <c r="C59" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60">
         <v>12847</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C60" t="s">
         <v>69</v>
       </c>
-      <c r="D59" t="s">
-        <v>7</v>
-      </c>
-      <c r="E59" t="s">
+      <c r="D60" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52508D7F-6AD3-4EB5-9937-74E6DD831796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC52565-423C-4D91-90FB-028695B51EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -667,7 +667,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 11047 / 동전0</v>
+        <v>Gold / 3190 / 뱀</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1636,7 +1636,7 @@
         <v>7</v>
       </c>
       <c r="E58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC52565-423C-4D91-90FB-028695B51EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA54264-10D5-4FCB-9631-679F64CACB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -667,7 +667,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 3190 / 뱀</v>
+        <v>Silver / 2217 / 로프</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1619,7 +1619,7 @@
         <v>7</v>
       </c>
       <c r="E57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA54264-10D5-4FCB-9631-679F64CACB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8421B787-2BF7-45FD-A6F8-D0CE62304AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="72">
   <si>
     <t>단계</t>
   </si>
@@ -279,6 +279,10 @@
   </si>
   <si>
     <t>부분합</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회전초밥</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -638,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -667,7 +671,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 2217 / 로프</v>
+        <v>Silver / 2559 / 수열</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1670,6 +1674,23 @@
         <v>7</v>
       </c>
       <c r="E60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61">
+        <v>2531</v>
+      </c>
+      <c r="C61" t="s">
+        <v>71</v>
+      </c>
+      <c r="D61" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8421B787-2BF7-45FD-A6F8-D0CE62304AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E654F998-F046-4F32-A6AB-DC4456D886BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="72">
   <si>
     <t>단계</t>
   </si>
@@ -642,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -667,11 +667,11 @@
       <c r="H1" s="1"/>
       <c r="I1" t="str" cm="1">
         <f t="array" aca="1" ref="I1" ca="1">_xlfn.LET(
-    _xlpm.reviewRows, _xlfn._xlws.FILTER(ROW(E2:E1001), E2:E1001="X"),
+    _xlpm.reviewRows, _xlfn._xlws.FILTER(ROW(E2:E1002), E2:E1002="X"),
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 2559 / 수열</v>
+        <v>Silver / 1789 / 수들의합</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -880,19 +880,19 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B14">
-        <v>1021</v>
+        <v>15961</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
@@ -900,10 +900,10 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>10431</v>
+        <v>1021</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -917,10 +917,10 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>10866</v>
+        <v>10431</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -934,10 +934,10 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>11279</v>
+        <v>10866</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -951,16 +951,16 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>11286</v>
+        <v>11279</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
@@ -968,16 +968,16 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>1138</v>
+        <v>11286</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
@@ -985,10 +985,10 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>1158</v>
+        <v>1138</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -1002,10 +1002,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>11723</v>
+        <v>1158</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -1019,10 +1019,10 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>11866</v>
+        <v>11723</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -1036,10 +1036,10 @@
         <v>20</v>
       </c>
       <c r="B23">
-        <v>1205</v>
+        <v>11866</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -1053,10 +1053,10 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>1244</v>
+        <v>1205</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -1070,10 +1070,10 @@
         <v>20</v>
       </c>
       <c r="B25">
-        <v>1260</v>
+        <v>1244</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -1087,10 +1087,10 @@
         <v>20</v>
       </c>
       <c r="B26">
-        <v>13305</v>
+        <v>1260</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -1104,10 +1104,10 @@
         <v>20</v>
       </c>
       <c r="B27">
-        <v>1406</v>
+        <v>13305</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -1121,10 +1121,10 @@
         <v>20</v>
       </c>
       <c r="B28">
-        <v>1417</v>
+        <v>1406</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -1138,16 +1138,16 @@
         <v>20</v>
       </c>
       <c r="B29">
-        <v>14940</v>
+        <v>1417</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
@@ -1155,16 +1155,16 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>1515</v>
+        <v>14940</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
@@ -1172,10 +1172,10 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>1654</v>
+        <v>1515</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -1189,10 +1189,10 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>17266</v>
+        <v>1654</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -1206,10 +1206,10 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>1927</v>
+        <v>17266</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -1223,10 +1223,10 @@
         <v>20</v>
       </c>
       <c r="B34">
-        <v>1931</v>
+        <v>1927</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -1240,10 +1240,10 @@
         <v>20</v>
       </c>
       <c r="B35">
-        <v>1966</v>
+        <v>1931</v>
       </c>
       <c r="C35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -1257,10 +1257,10 @@
         <v>20</v>
       </c>
       <c r="B36">
-        <v>20006</v>
+        <v>1966</v>
       </c>
       <c r="C36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -1274,10 +1274,10 @@
         <v>20</v>
       </c>
       <c r="B37">
-        <v>2075</v>
+        <v>20006</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -1291,10 +1291,10 @@
         <v>20</v>
       </c>
       <c r="B38">
-        <v>20922</v>
+        <v>2075</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -1308,10 +1308,10 @@
         <v>20</v>
       </c>
       <c r="B39">
-        <v>2164</v>
+        <v>20922</v>
       </c>
       <c r="C39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -1325,10 +1325,10 @@
         <v>20</v>
       </c>
       <c r="B40">
-        <v>2346</v>
+        <v>2164</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -1342,10 +1342,10 @@
         <v>20</v>
       </c>
       <c r="B41">
-        <v>2512</v>
+        <v>2346</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -1359,10 +1359,10 @@
         <v>20</v>
       </c>
       <c r="B42">
-        <v>25757</v>
+        <v>2512</v>
       </c>
       <c r="C42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -1376,10 +1376,10 @@
         <v>20</v>
       </c>
       <c r="B43">
-        <v>2805</v>
+        <v>25757</v>
       </c>
       <c r="C43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -1393,10 +1393,10 @@
         <v>20</v>
       </c>
       <c r="B44">
-        <v>4659</v>
+        <v>2805</v>
       </c>
       <c r="C44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -1410,10 +1410,10 @@
         <v>20</v>
       </c>
       <c r="B45">
-        <v>5397</v>
+        <v>4659</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -1427,10 +1427,10 @@
         <v>20</v>
       </c>
       <c r="B46">
-        <v>6236</v>
+        <v>5397</v>
       </c>
       <c r="C46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -1444,10 +1444,10 @@
         <v>20</v>
       </c>
       <c r="B47">
-        <v>7568</v>
+        <v>6236</v>
       </c>
       <c r="C47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -1461,10 +1461,10 @@
         <v>20</v>
       </c>
       <c r="B48">
-        <v>8979</v>
+        <v>7568</v>
       </c>
       <c r="C48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -1478,10 +1478,10 @@
         <v>20</v>
       </c>
       <c r="B49">
-        <v>9655</v>
+        <v>8979</v>
       </c>
       <c r="C49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -1495,10 +1495,10 @@
         <v>20</v>
       </c>
       <c r="B50">
-        <v>1541</v>
+        <v>9655</v>
       </c>
       <c r="C50" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -1512,10 +1512,10 @@
         <v>20</v>
       </c>
       <c r="B51">
-        <v>11399</v>
+        <v>1541</v>
       </c>
       <c r="C51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -1529,16 +1529,16 @@
         <v>20</v>
       </c>
       <c r="B52">
-        <v>1789</v>
+        <v>11399</v>
       </c>
       <c r="C52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
       </c>
       <c r="E52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
@@ -1546,10 +1546,10 @@
         <v>20</v>
       </c>
       <c r="B53">
-        <v>11047</v>
+        <v>1789</v>
       </c>
       <c r="C53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -1563,10 +1563,10 @@
         <v>20</v>
       </c>
       <c r="B54">
-        <v>2217</v>
+        <v>11047</v>
       </c>
       <c r="C54" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -1580,10 +1580,10 @@
         <v>20</v>
       </c>
       <c r="B55">
-        <v>9017</v>
+        <v>2217</v>
       </c>
       <c r="C55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -1597,10 +1597,10 @@
         <v>20</v>
       </c>
       <c r="B56">
-        <v>1026</v>
+        <v>9017</v>
       </c>
       <c r="C56" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -1614,16 +1614,16 @@
         <v>20</v>
       </c>
       <c r="B57">
-        <v>2563</v>
+        <v>1026</v>
       </c>
       <c r="C57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
       </c>
       <c r="E57" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
@@ -1631,10 +1631,10 @@
         <v>20</v>
       </c>
       <c r="B58">
-        <v>21921</v>
+        <v>2563</v>
       </c>
       <c r="C58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -1648,16 +1648,16 @@
         <v>20</v>
       </c>
       <c r="B59">
-        <v>2559</v>
+        <v>21921</v>
       </c>
       <c r="C59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
       </c>
       <c r="E59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
@@ -1665,10 +1665,10 @@
         <v>20</v>
       </c>
       <c r="B60">
-        <v>12847</v>
+        <v>2559</v>
       </c>
       <c r="C60" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -1682,15 +1682,32 @@
         <v>20</v>
       </c>
       <c r="B61">
+        <v>12847</v>
+      </c>
+      <c r="C61" t="s">
+        <v>69</v>
+      </c>
+      <c r="D61" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>20</v>
+      </c>
+      <c r="B62">
         <v>2531</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C62" t="s">
         <v>71</v>
       </c>
-      <c r="D61" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="D62" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E654F998-F046-4F32-A6AB-DC4456D886BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A897AC75-0AE9-4F42-A3F0-D193DA11E266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="73">
   <si>
     <t>단계</t>
   </si>
@@ -283,6 +283,10 @@
   </si>
   <si>
     <t>회전초밥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게으른 백곰</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -642,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -671,7 +675,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1789 / 수들의합</v>
+        <v>Silver / 14940 / 쉬운최단거리</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1708,6 +1712,23 @@
         <v>7</v>
       </c>
       <c r="E62" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>20</v>
+      </c>
+      <c r="B63">
+        <v>10025</v>
+      </c>
+      <c r="C63" t="s">
+        <v>72</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A897AC75-0AE9-4F42-A3F0-D193DA11E266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15575922-C68E-4F4A-8D4F-70972DA0188E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="74">
   <si>
     <t>단계</t>
   </si>
@@ -287,6 +287,10 @@
   </si>
   <si>
     <t>게으른 백곰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도둑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -646,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -671,11 +675,11 @@
       <c r="H1" s="1"/>
       <c r="I1" t="str" cm="1">
         <f t="array" aca="1" ref="I1" ca="1">_xlfn.LET(
-    _xlpm.reviewRows, _xlfn._xlws.FILTER(ROW(E2:E1002), E2:E1002="X"),
+    _xlpm.reviewRows, _xlfn._xlws.FILTER(ROW(E2:E1003), E2:E1003="X"),
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 14940 / 쉬운최단거리</v>
+        <v>Silver / 1789 / 수들의합</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -901,19 +905,19 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B15">
-        <v>1021</v>
+        <v>13422</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
@@ -921,10 +925,10 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>10431</v>
+        <v>1021</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -938,10 +942,10 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>10866</v>
+        <v>10431</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -955,10 +959,10 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>11279</v>
+        <v>10866</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -972,16 +976,16 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>11286</v>
+        <v>11279</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
@@ -989,16 +993,16 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>1138</v>
+        <v>11286</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
@@ -1006,10 +1010,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1158</v>
+        <v>1138</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -1023,10 +1027,10 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>11723</v>
+        <v>1158</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -1040,10 +1044,10 @@
         <v>20</v>
       </c>
       <c r="B23">
-        <v>11866</v>
+        <v>11723</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -1057,10 +1061,10 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>1205</v>
+        <v>11866</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -1074,10 +1078,10 @@
         <v>20</v>
       </c>
       <c r="B25">
-        <v>1244</v>
+        <v>1205</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -1091,10 +1095,10 @@
         <v>20</v>
       </c>
       <c r="B26">
-        <v>1260</v>
+        <v>1244</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -1108,10 +1112,10 @@
         <v>20</v>
       </c>
       <c r="B27">
-        <v>13305</v>
+        <v>1260</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -1125,10 +1129,10 @@
         <v>20</v>
       </c>
       <c r="B28">
-        <v>1406</v>
+        <v>13305</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -1142,10 +1146,10 @@
         <v>20</v>
       </c>
       <c r="B29">
-        <v>1417</v>
+        <v>1406</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -1159,16 +1163,16 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>14940</v>
+        <v>1417</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
@@ -1176,16 +1180,16 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>1515</v>
+        <v>14940</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
@@ -1193,10 +1197,10 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>1654</v>
+        <v>1515</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -1210,10 +1214,10 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>17266</v>
+        <v>1654</v>
       </c>
       <c r="C33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -1227,10 +1231,10 @@
         <v>20</v>
       </c>
       <c r="B34">
-        <v>1927</v>
+        <v>17266</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -1244,10 +1248,10 @@
         <v>20</v>
       </c>
       <c r="B35">
-        <v>1931</v>
+        <v>1927</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -1261,10 +1265,10 @@
         <v>20</v>
       </c>
       <c r="B36">
-        <v>1966</v>
+        <v>1931</v>
       </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -1278,10 +1282,10 @@
         <v>20</v>
       </c>
       <c r="B37">
-        <v>20006</v>
+        <v>1966</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -1295,10 +1299,10 @@
         <v>20</v>
       </c>
       <c r="B38">
-        <v>2075</v>
+        <v>20006</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -1312,10 +1316,10 @@
         <v>20</v>
       </c>
       <c r="B39">
-        <v>20922</v>
+        <v>2075</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -1329,10 +1333,10 @@
         <v>20</v>
       </c>
       <c r="B40">
-        <v>2164</v>
+        <v>20922</v>
       </c>
       <c r="C40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -1346,10 +1350,10 @@
         <v>20</v>
       </c>
       <c r="B41">
-        <v>2346</v>
+        <v>2164</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -1363,10 +1367,10 @@
         <v>20</v>
       </c>
       <c r="B42">
-        <v>2512</v>
+        <v>2346</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -1380,10 +1384,10 @@
         <v>20</v>
       </c>
       <c r="B43">
-        <v>25757</v>
+        <v>2512</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -1397,10 +1401,10 @@
         <v>20</v>
       </c>
       <c r="B44">
-        <v>2805</v>
+        <v>25757</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -1414,10 +1418,10 @@
         <v>20</v>
       </c>
       <c r="B45">
-        <v>4659</v>
+        <v>2805</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -1431,10 +1435,10 @@
         <v>20</v>
       </c>
       <c r="B46">
-        <v>5397</v>
+        <v>4659</v>
       </c>
       <c r="C46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -1448,10 +1452,10 @@
         <v>20</v>
       </c>
       <c r="B47">
-        <v>6236</v>
+        <v>5397</v>
       </c>
       <c r="C47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -1465,10 +1469,10 @@
         <v>20</v>
       </c>
       <c r="B48">
-        <v>7568</v>
+        <v>6236</v>
       </c>
       <c r="C48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -1482,10 +1486,10 @@
         <v>20</v>
       </c>
       <c r="B49">
-        <v>8979</v>
+        <v>7568</v>
       </c>
       <c r="C49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -1499,10 +1503,10 @@
         <v>20</v>
       </c>
       <c r="B50">
-        <v>9655</v>
+        <v>8979</v>
       </c>
       <c r="C50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -1516,10 +1520,10 @@
         <v>20</v>
       </c>
       <c r="B51">
-        <v>1541</v>
+        <v>9655</v>
       </c>
       <c r="C51" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -1533,10 +1537,10 @@
         <v>20</v>
       </c>
       <c r="B52">
-        <v>11399</v>
+        <v>1541</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -1550,16 +1554,16 @@
         <v>20</v>
       </c>
       <c r="B53">
-        <v>1789</v>
+        <v>11399</v>
       </c>
       <c r="C53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
       </c>
       <c r="E53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
@@ -1567,10 +1571,10 @@
         <v>20</v>
       </c>
       <c r="B54">
-        <v>11047</v>
+        <v>1789</v>
       </c>
       <c r="C54" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -1584,10 +1588,10 @@
         <v>20</v>
       </c>
       <c r="B55">
-        <v>2217</v>
+        <v>11047</v>
       </c>
       <c r="C55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -1601,10 +1605,10 @@
         <v>20</v>
       </c>
       <c r="B56">
-        <v>9017</v>
+        <v>2217</v>
       </c>
       <c r="C56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -1618,10 +1622,10 @@
         <v>20</v>
       </c>
       <c r="B57">
-        <v>1026</v>
+        <v>9017</v>
       </c>
       <c r="C57" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -1635,16 +1639,16 @@
         <v>20</v>
       </c>
       <c r="B58">
-        <v>2563</v>
+        <v>1026</v>
       </c>
       <c r="C58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
       </c>
       <c r="E58" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
@@ -1652,10 +1656,10 @@
         <v>20</v>
       </c>
       <c r="B59">
-        <v>21921</v>
+        <v>2563</v>
       </c>
       <c r="C59" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -1669,16 +1673,16 @@
         <v>20</v>
       </c>
       <c r="B60">
-        <v>2559</v>
+        <v>21921</v>
       </c>
       <c r="C60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
       </c>
       <c r="E60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
@@ -1686,10 +1690,10 @@
         <v>20</v>
       </c>
       <c r="B61">
-        <v>12847</v>
+        <v>2559</v>
       </c>
       <c r="C61" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -1703,10 +1707,10 @@
         <v>20</v>
       </c>
       <c r="B62">
-        <v>2531</v>
+        <v>12847</v>
       </c>
       <c r="C62" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -1720,15 +1724,32 @@
         <v>20</v>
       </c>
       <c r="B63">
+        <v>2531</v>
+      </c>
+      <c r="C63" t="s">
+        <v>71</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>20</v>
+      </c>
+      <c r="B64">
         <v>10025</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C64" t="s">
         <v>72</v>
       </c>
-      <c r="D63" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="D64" t="s">
+        <v>7</v>
+      </c>
+      <c r="E64" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15575922-C68E-4F4A-8D4F-70972DA0188E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC046DF-8151-40D5-8819-0113F6CDDC0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="75">
   <si>
     <t>단계</t>
   </si>
@@ -291,6 +291,10 @@
   </si>
   <si>
     <t>도둑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>용액</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -650,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -675,11 +679,11 @@
       <c r="H1" s="1"/>
       <c r="I1" t="str" cm="1">
         <f t="array" aca="1" ref="I1" ca="1">_xlfn.LET(
-    _xlpm.reviewRows, _xlfn._xlws.FILTER(ROW(E2:E1003), E2:E1003="X"),
+    _xlpm.reviewRows, _xlfn._xlws.FILTER(ROW(E2:E1004), E2:E1004="X"),
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1789 / 수들의합</v>
+        <v>Gold / 2467 / 용액</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -922,19 +926,19 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B16">
-        <v>1021</v>
+        <v>2467</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
@@ -942,10 +946,10 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>10431</v>
+        <v>1021</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -959,10 +963,10 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>10866</v>
+        <v>10431</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -976,10 +980,10 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>11279</v>
+        <v>10866</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -993,16 +997,16 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>11286</v>
+        <v>11279</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
@@ -1010,16 +1014,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1138</v>
+        <v>11286</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
@@ -1027,10 +1031,10 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>1158</v>
+        <v>1138</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -1044,10 +1048,10 @@
         <v>20</v>
       </c>
       <c r="B23">
-        <v>11723</v>
+        <v>1158</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -1061,10 +1065,10 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>11866</v>
+        <v>11723</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -1078,10 +1082,10 @@
         <v>20</v>
       </c>
       <c r="B25">
-        <v>1205</v>
+        <v>11866</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -1095,10 +1099,10 @@
         <v>20</v>
       </c>
       <c r="B26">
-        <v>1244</v>
+        <v>1205</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -1112,10 +1116,10 @@
         <v>20</v>
       </c>
       <c r="B27">
-        <v>1260</v>
+        <v>1244</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -1129,10 +1133,10 @@
         <v>20</v>
       </c>
       <c r="B28">
-        <v>13305</v>
+        <v>1260</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -1146,10 +1150,10 @@
         <v>20</v>
       </c>
       <c r="B29">
-        <v>1406</v>
+        <v>13305</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -1163,10 +1167,10 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>1417</v>
+        <v>1406</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -1180,16 +1184,16 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>14940</v>
+        <v>1417</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
@@ -1197,16 +1201,16 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>1515</v>
+        <v>14940</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
@@ -1214,10 +1218,10 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>1654</v>
+        <v>1515</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -1231,10 +1235,10 @@
         <v>20</v>
       </c>
       <c r="B34">
-        <v>17266</v>
+        <v>1654</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -1248,10 +1252,10 @@
         <v>20</v>
       </c>
       <c r="B35">
-        <v>1927</v>
+        <v>17266</v>
       </c>
       <c r="C35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -1265,10 +1269,10 @@
         <v>20</v>
       </c>
       <c r="B36">
-        <v>1931</v>
+        <v>1927</v>
       </c>
       <c r="C36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -1282,10 +1286,10 @@
         <v>20</v>
       </c>
       <c r="B37">
-        <v>1966</v>
+        <v>1931</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -1299,10 +1303,10 @@
         <v>20</v>
       </c>
       <c r="B38">
-        <v>20006</v>
+        <v>1966</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -1316,10 +1320,10 @@
         <v>20</v>
       </c>
       <c r="B39">
-        <v>2075</v>
+        <v>20006</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -1333,10 +1337,10 @@
         <v>20</v>
       </c>
       <c r="B40">
-        <v>20922</v>
+        <v>2075</v>
       </c>
       <c r="C40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -1350,10 +1354,10 @@
         <v>20</v>
       </c>
       <c r="B41">
-        <v>2164</v>
+        <v>20922</v>
       </c>
       <c r="C41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -1367,10 +1371,10 @@
         <v>20</v>
       </c>
       <c r="B42">
-        <v>2346</v>
+        <v>2164</v>
       </c>
       <c r="C42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -1384,10 +1388,10 @@
         <v>20</v>
       </c>
       <c r="B43">
-        <v>2512</v>
+        <v>2346</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -1401,10 +1405,10 @@
         <v>20</v>
       </c>
       <c r="B44">
-        <v>25757</v>
+        <v>2512</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -1418,10 +1422,10 @@
         <v>20</v>
       </c>
       <c r="B45">
-        <v>2805</v>
+        <v>25757</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -1435,10 +1439,10 @@
         <v>20</v>
       </c>
       <c r="B46">
-        <v>4659</v>
+        <v>2805</v>
       </c>
       <c r="C46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -1452,10 +1456,10 @@
         <v>20</v>
       </c>
       <c r="B47">
-        <v>5397</v>
+        <v>4659</v>
       </c>
       <c r="C47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -1469,10 +1473,10 @@
         <v>20</v>
       </c>
       <c r="B48">
-        <v>6236</v>
+        <v>5397</v>
       </c>
       <c r="C48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -1486,10 +1490,10 @@
         <v>20</v>
       </c>
       <c r="B49">
-        <v>7568</v>
+        <v>6236</v>
       </c>
       <c r="C49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -1503,10 +1507,10 @@
         <v>20</v>
       </c>
       <c r="B50">
-        <v>8979</v>
+        <v>7568</v>
       </c>
       <c r="C50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -1520,10 +1524,10 @@
         <v>20</v>
       </c>
       <c r="B51">
-        <v>9655</v>
+        <v>8979</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -1537,10 +1541,10 @@
         <v>20</v>
       </c>
       <c r="B52">
-        <v>1541</v>
+        <v>9655</v>
       </c>
       <c r="C52" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -1554,10 +1558,10 @@
         <v>20</v>
       </c>
       <c r="B53">
-        <v>11399</v>
+        <v>1541</v>
       </c>
       <c r="C53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -1571,16 +1575,16 @@
         <v>20</v>
       </c>
       <c r="B54">
-        <v>1789</v>
+        <v>11399</v>
       </c>
       <c r="C54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
       </c>
       <c r="E54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
@@ -1588,10 +1592,10 @@
         <v>20</v>
       </c>
       <c r="B55">
-        <v>11047</v>
+        <v>1789</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -1605,10 +1609,10 @@
         <v>20</v>
       </c>
       <c r="B56">
-        <v>2217</v>
+        <v>11047</v>
       </c>
       <c r="C56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -1622,10 +1626,10 @@
         <v>20</v>
       </c>
       <c r="B57">
-        <v>9017</v>
+        <v>2217</v>
       </c>
       <c r="C57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -1639,10 +1643,10 @@
         <v>20</v>
       </c>
       <c r="B58">
-        <v>1026</v>
+        <v>9017</v>
       </c>
       <c r="C58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -1656,16 +1660,16 @@
         <v>20</v>
       </c>
       <c r="B59">
-        <v>2563</v>
+        <v>1026</v>
       </c>
       <c r="C59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
       </c>
       <c r="E59" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
@@ -1673,10 +1677,10 @@
         <v>20</v>
       </c>
       <c r="B60">
-        <v>21921</v>
+        <v>2563</v>
       </c>
       <c r="C60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -1690,16 +1694,16 @@
         <v>20</v>
       </c>
       <c r="B61">
-        <v>2559</v>
+        <v>21921</v>
       </c>
       <c r="C61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
@@ -1707,10 +1711,10 @@
         <v>20</v>
       </c>
       <c r="B62">
-        <v>12847</v>
+        <v>2559</v>
       </c>
       <c r="C62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -1724,10 +1728,10 @@
         <v>20</v>
       </c>
       <c r="B63">
-        <v>2531</v>
+        <v>12847</v>
       </c>
       <c r="C63" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -1741,15 +1745,32 @@
         <v>20</v>
       </c>
       <c r="B64">
+        <v>2531</v>
+      </c>
+      <c r="C64" t="s">
+        <v>71</v>
+      </c>
+      <c r="D64" t="s">
+        <v>7</v>
+      </c>
+      <c r="E64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>20</v>
+      </c>
+      <c r="B65">
         <v>10025</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C65" t="s">
         <v>72</v>
       </c>
-      <c r="D64" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="D65" t="s">
+        <v>7</v>
+      </c>
+      <c r="E65" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC046DF-8151-40D5-8819-0113F6CDDC0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC35B98E-85B6-4EB1-A451-8AB09FC25E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="76">
   <si>
     <t>단계</t>
   </si>
@@ -295,6 +295,10 @@
   </si>
   <si>
     <t>용액</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두용액</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -654,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -679,11 +683,11 @@
       <c r="H1" s="1"/>
       <c r="I1" t="str" cm="1">
         <f t="array" aca="1" ref="I1" ca="1">_xlfn.LET(
-    _xlpm.reviewRows, _xlfn._xlws.FILTER(ROW(E2:E1004), E2:E1004="X"),
+    _xlpm.reviewRows, _xlfn._xlws.FILTER(ROW(E2:E1005), E2:E1005="X"),
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 2467 / 용액</v>
+        <v>Silver / 1789 / 수들의합</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -943,19 +947,19 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B17">
-        <v>1021</v>
+        <v>2470</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
@@ -963,10 +967,10 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>10431</v>
+        <v>1021</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -980,10 +984,10 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>10866</v>
+        <v>10431</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -997,10 +1001,10 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>11279</v>
+        <v>10866</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -1014,16 +1018,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>11286</v>
+        <v>11279</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
@@ -1031,16 +1035,16 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>1138</v>
+        <v>11286</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
@@ -1048,10 +1052,10 @@
         <v>20</v>
       </c>
       <c r="B23">
-        <v>1158</v>
+        <v>1138</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -1065,10 +1069,10 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>11723</v>
+        <v>1158</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -1082,10 +1086,10 @@
         <v>20</v>
       </c>
       <c r="B25">
-        <v>11866</v>
+        <v>11723</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -1099,10 +1103,10 @@
         <v>20</v>
       </c>
       <c r="B26">
-        <v>1205</v>
+        <v>11866</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -1116,10 +1120,10 @@
         <v>20</v>
       </c>
       <c r="B27">
-        <v>1244</v>
+        <v>1205</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -1133,10 +1137,10 @@
         <v>20</v>
       </c>
       <c r="B28">
-        <v>1260</v>
+        <v>1244</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -1150,10 +1154,10 @@
         <v>20</v>
       </c>
       <c r="B29">
-        <v>13305</v>
+        <v>1260</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -1167,10 +1171,10 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>1406</v>
+        <v>13305</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -1184,10 +1188,10 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>1417</v>
+        <v>1406</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -1201,16 +1205,16 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>14940</v>
+        <v>1417</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
@@ -1218,16 +1222,16 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>1515</v>
+        <v>14940</v>
       </c>
       <c r="C33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
@@ -1235,10 +1239,10 @@
         <v>20</v>
       </c>
       <c r="B34">
-        <v>1654</v>
+        <v>1515</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -1252,10 +1256,10 @@
         <v>20</v>
       </c>
       <c r="B35">
-        <v>17266</v>
+        <v>1654</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -1269,10 +1273,10 @@
         <v>20</v>
       </c>
       <c r="B36">
-        <v>1927</v>
+        <v>17266</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -1286,10 +1290,10 @@
         <v>20</v>
       </c>
       <c r="B37">
-        <v>1931</v>
+        <v>1927</v>
       </c>
       <c r="C37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -1303,10 +1307,10 @@
         <v>20</v>
       </c>
       <c r="B38">
-        <v>1966</v>
+        <v>1931</v>
       </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -1320,10 +1324,10 @@
         <v>20</v>
       </c>
       <c r="B39">
-        <v>20006</v>
+        <v>1966</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -1337,10 +1341,10 @@
         <v>20</v>
       </c>
       <c r="B40">
-        <v>2075</v>
+        <v>20006</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -1354,10 +1358,10 @@
         <v>20</v>
       </c>
       <c r="B41">
-        <v>20922</v>
+        <v>2075</v>
       </c>
       <c r="C41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -1371,10 +1375,10 @@
         <v>20</v>
       </c>
       <c r="B42">
-        <v>2164</v>
+        <v>20922</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -1388,10 +1392,10 @@
         <v>20</v>
       </c>
       <c r="B43">
-        <v>2346</v>
+        <v>2164</v>
       </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -1405,10 +1409,10 @@
         <v>20</v>
       </c>
       <c r="B44">
-        <v>2512</v>
+        <v>2346</v>
       </c>
       <c r="C44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -1422,10 +1426,10 @@
         <v>20</v>
       </c>
       <c r="B45">
-        <v>25757</v>
+        <v>2512</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -1439,10 +1443,10 @@
         <v>20</v>
       </c>
       <c r="B46">
-        <v>2805</v>
+        <v>25757</v>
       </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -1456,10 +1460,10 @@
         <v>20</v>
       </c>
       <c r="B47">
-        <v>4659</v>
+        <v>2805</v>
       </c>
       <c r="C47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -1473,10 +1477,10 @@
         <v>20</v>
       </c>
       <c r="B48">
-        <v>5397</v>
+        <v>4659</v>
       </c>
       <c r="C48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -1490,10 +1494,10 @@
         <v>20</v>
       </c>
       <c r="B49">
-        <v>6236</v>
+        <v>5397</v>
       </c>
       <c r="C49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -1507,10 +1511,10 @@
         <v>20</v>
       </c>
       <c r="B50">
-        <v>7568</v>
+        <v>6236</v>
       </c>
       <c r="C50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -1524,10 +1528,10 @@
         <v>20</v>
       </c>
       <c r="B51">
-        <v>8979</v>
+        <v>7568</v>
       </c>
       <c r="C51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -1541,10 +1545,10 @@
         <v>20</v>
       </c>
       <c r="B52">
-        <v>9655</v>
+        <v>8979</v>
       </c>
       <c r="C52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -1558,10 +1562,10 @@
         <v>20</v>
       </c>
       <c r="B53">
-        <v>1541</v>
+        <v>9655</v>
       </c>
       <c r="C53" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -1575,10 +1579,10 @@
         <v>20</v>
       </c>
       <c r="B54">
-        <v>11399</v>
+        <v>1541</v>
       </c>
       <c r="C54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -1592,16 +1596,16 @@
         <v>20</v>
       </c>
       <c r="B55">
-        <v>1789</v>
+        <v>11399</v>
       </c>
       <c r="C55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
       </c>
       <c r="E55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
@@ -1609,10 +1613,10 @@
         <v>20</v>
       </c>
       <c r="B56">
-        <v>11047</v>
+        <v>1789</v>
       </c>
       <c r="C56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -1626,10 +1630,10 @@
         <v>20</v>
       </c>
       <c r="B57">
-        <v>2217</v>
+        <v>11047</v>
       </c>
       <c r="C57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -1643,10 +1647,10 @@
         <v>20</v>
       </c>
       <c r="B58">
-        <v>9017</v>
+        <v>2217</v>
       </c>
       <c r="C58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -1660,10 +1664,10 @@
         <v>20</v>
       </c>
       <c r="B59">
-        <v>1026</v>
+        <v>9017</v>
       </c>
       <c r="C59" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -1677,16 +1681,16 @@
         <v>20</v>
       </c>
       <c r="B60">
-        <v>2563</v>
+        <v>1026</v>
       </c>
       <c r="C60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
       </c>
       <c r="E60" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
@@ -1694,10 +1698,10 @@
         <v>20</v>
       </c>
       <c r="B61">
-        <v>21921</v>
+        <v>2563</v>
       </c>
       <c r="C61" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -1711,16 +1715,16 @@
         <v>20</v>
       </c>
       <c r="B62">
-        <v>2559</v>
+        <v>21921</v>
       </c>
       <c r="C62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
       </c>
       <c r="E62" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
@@ -1728,10 +1732,10 @@
         <v>20</v>
       </c>
       <c r="B63">
-        <v>12847</v>
+        <v>2559</v>
       </c>
       <c r="C63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -1745,10 +1749,10 @@
         <v>20</v>
       </c>
       <c r="B64">
-        <v>2531</v>
+        <v>12847</v>
       </c>
       <c r="C64" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -1762,15 +1766,32 @@
         <v>20</v>
       </c>
       <c r="B65">
+        <v>2531</v>
+      </c>
+      <c r="C65" t="s">
+        <v>71</v>
+      </c>
+      <c r="D65" t="s">
+        <v>7</v>
+      </c>
+      <c r="E65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>20</v>
+      </c>
+      <c r="B66">
         <v>10025</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C66" t="s">
         <v>72</v>
       </c>
-      <c r="D65" t="s">
-        <v>7</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
+      <c r="E66" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC35B98E-85B6-4EB1-A451-8AB09FC25E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B5BD06-748C-4542-9081-0E04959E2F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="77">
   <si>
     <t>단계</t>
   </si>
@@ -299,6 +299,10 @@
   </si>
   <si>
     <t>두용액</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -658,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -683,11 +687,11 @@
       <c r="H1" s="1"/>
       <c r="I1" t="str" cm="1">
         <f t="array" aca="1" ref="I1" ca="1">_xlfn.LET(
-    _xlpm.reviewRows, _xlfn._xlws.FILTER(ROW(E2:E1005), E2:E1005="X"),
+    _xlpm.reviewRows, _xlfn._xlws.FILTER(ROW(E2:E1006), E2:E1006="X"),
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1789 / 수들의합</v>
+        <v>Silver / 2531 / 회전초밥</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -964,19 +968,19 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B18">
-        <v>1021</v>
+        <v>1253</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
@@ -984,10 +988,10 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>10431</v>
+        <v>1021</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -1001,10 +1005,10 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>10866</v>
+        <v>10431</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -1018,10 +1022,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>11279</v>
+        <v>10866</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -1035,16 +1039,16 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>11286</v>
+        <v>11279</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
@@ -1052,16 +1056,16 @@
         <v>20</v>
       </c>
       <c r="B23">
-        <v>1138</v>
+        <v>11286</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
@@ -1069,10 +1073,10 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>1158</v>
+        <v>1138</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -1086,10 +1090,10 @@
         <v>20</v>
       </c>
       <c r="B25">
-        <v>11723</v>
+        <v>1158</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -1103,10 +1107,10 @@
         <v>20</v>
       </c>
       <c r="B26">
-        <v>11866</v>
+        <v>11723</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -1120,10 +1124,10 @@
         <v>20</v>
       </c>
       <c r="B27">
-        <v>1205</v>
+        <v>11866</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -1137,10 +1141,10 @@
         <v>20</v>
       </c>
       <c r="B28">
-        <v>1244</v>
+        <v>1205</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -1154,10 +1158,10 @@
         <v>20</v>
       </c>
       <c r="B29">
-        <v>1260</v>
+        <v>1244</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -1171,10 +1175,10 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>13305</v>
+        <v>1260</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -1188,10 +1192,10 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>1406</v>
+        <v>13305</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -1205,10 +1209,10 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>1417</v>
+        <v>1406</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -1222,16 +1226,16 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>14940</v>
+        <v>1417</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
@@ -1239,16 +1243,16 @@
         <v>20</v>
       </c>
       <c r="B34">
-        <v>1515</v>
+        <v>14940</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
@@ -1256,10 +1260,10 @@
         <v>20</v>
       </c>
       <c r="B35">
-        <v>1654</v>
+        <v>1515</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -1273,10 +1277,10 @@
         <v>20</v>
       </c>
       <c r="B36">
-        <v>17266</v>
+        <v>1654</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -1290,10 +1294,10 @@
         <v>20</v>
       </c>
       <c r="B37">
-        <v>1927</v>
+        <v>17266</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -1307,10 +1311,10 @@
         <v>20</v>
       </c>
       <c r="B38">
-        <v>1931</v>
+        <v>1927</v>
       </c>
       <c r="C38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -1324,10 +1328,10 @@
         <v>20</v>
       </c>
       <c r="B39">
-        <v>1966</v>
+        <v>1931</v>
       </c>
       <c r="C39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -1341,10 +1345,10 @@
         <v>20</v>
       </c>
       <c r="B40">
-        <v>20006</v>
+        <v>1966</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -1358,10 +1362,10 @@
         <v>20</v>
       </c>
       <c r="B41">
-        <v>2075</v>
+        <v>20006</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -1375,10 +1379,10 @@
         <v>20</v>
       </c>
       <c r="B42">
-        <v>20922</v>
+        <v>2075</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -1392,10 +1396,10 @@
         <v>20</v>
       </c>
       <c r="B43">
-        <v>2164</v>
+        <v>20922</v>
       </c>
       <c r="C43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -1409,10 +1413,10 @@
         <v>20</v>
       </c>
       <c r="B44">
-        <v>2346</v>
+        <v>2164</v>
       </c>
       <c r="C44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -1426,10 +1430,10 @@
         <v>20</v>
       </c>
       <c r="B45">
-        <v>2512</v>
+        <v>2346</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -1443,10 +1447,10 @@
         <v>20</v>
       </c>
       <c r="B46">
-        <v>25757</v>
+        <v>2512</v>
       </c>
       <c r="C46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -1460,10 +1464,10 @@
         <v>20</v>
       </c>
       <c r="B47">
-        <v>2805</v>
+        <v>25757</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -1477,10 +1481,10 @@
         <v>20</v>
       </c>
       <c r="B48">
-        <v>4659</v>
+        <v>2805</v>
       </c>
       <c r="C48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -1494,10 +1498,10 @@
         <v>20</v>
       </c>
       <c r="B49">
-        <v>5397</v>
+        <v>4659</v>
       </c>
       <c r="C49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -1511,10 +1515,10 @@
         <v>20</v>
       </c>
       <c r="B50">
-        <v>6236</v>
+        <v>5397</v>
       </c>
       <c r="C50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -1528,10 +1532,10 @@
         <v>20</v>
       </c>
       <c r="B51">
-        <v>7568</v>
+        <v>6236</v>
       </c>
       <c r="C51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -1545,10 +1549,10 @@
         <v>20</v>
       </c>
       <c r="B52">
-        <v>8979</v>
+        <v>7568</v>
       </c>
       <c r="C52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -1562,10 +1566,10 @@
         <v>20</v>
       </c>
       <c r="B53">
-        <v>9655</v>
+        <v>8979</v>
       </c>
       <c r="C53" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -1579,10 +1583,10 @@
         <v>20</v>
       </c>
       <c r="B54">
-        <v>1541</v>
+        <v>9655</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -1596,10 +1600,10 @@
         <v>20</v>
       </c>
       <c r="B55">
-        <v>11399</v>
+        <v>1541</v>
       </c>
       <c r="C55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -1613,16 +1617,16 @@
         <v>20</v>
       </c>
       <c r="B56">
-        <v>1789</v>
+        <v>11399</v>
       </c>
       <c r="C56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
       </c>
       <c r="E56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
@@ -1630,10 +1634,10 @@
         <v>20</v>
       </c>
       <c r="B57">
-        <v>11047</v>
+        <v>1789</v>
       </c>
       <c r="C57" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -1647,10 +1651,10 @@
         <v>20</v>
       </c>
       <c r="B58">
-        <v>2217</v>
+        <v>11047</v>
       </c>
       <c r="C58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -1664,10 +1668,10 @@
         <v>20</v>
       </c>
       <c r="B59">
-        <v>9017</v>
+        <v>2217</v>
       </c>
       <c r="C59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -1681,10 +1685,10 @@
         <v>20</v>
       </c>
       <c r="B60">
-        <v>1026</v>
+        <v>9017</v>
       </c>
       <c r="C60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -1698,16 +1702,16 @@
         <v>20</v>
       </c>
       <c r="B61">
-        <v>2563</v>
+        <v>1026</v>
       </c>
       <c r="C61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
@@ -1715,10 +1719,10 @@
         <v>20</v>
       </c>
       <c r="B62">
-        <v>21921</v>
+        <v>2563</v>
       </c>
       <c r="C62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -1732,16 +1736,16 @@
         <v>20</v>
       </c>
       <c r="B63">
-        <v>2559</v>
+        <v>21921</v>
       </c>
       <c r="C63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
       </c>
       <c r="E63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
@@ -1749,10 +1753,10 @@
         <v>20</v>
       </c>
       <c r="B64">
-        <v>12847</v>
+        <v>2559</v>
       </c>
       <c r="C64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -1766,10 +1770,10 @@
         <v>20</v>
       </c>
       <c r="B65">
-        <v>2531</v>
+        <v>12847</v>
       </c>
       <c r="C65" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -1783,15 +1787,32 @@
         <v>20</v>
       </c>
       <c r="B66">
+        <v>2531</v>
+      </c>
+      <c r="C66" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
+      <c r="E66" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>20</v>
+      </c>
+      <c r="B67">
         <v>10025</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C67" t="s">
         <v>72</v>
       </c>
-      <c r="D66" t="s">
-        <v>7</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="D67" t="s">
+        <v>7</v>
+      </c>
+      <c r="E67" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B5BD06-748C-4542-9081-0E04959E2F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D25AC1-EF9B-4711-A824-D94D34F3D12B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="78">
   <si>
     <t>단계</t>
   </si>
@@ -303,6 +303,10 @@
   </si>
   <si>
     <t>좋다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수고르기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -662,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -687,11 +691,11 @@
       <c r="H1" s="1"/>
       <c r="I1" t="str" cm="1">
         <f t="array" aca="1" ref="I1" ca="1">_xlfn.LET(
-    _xlpm.reviewRows, _xlfn._xlws.FILTER(ROW(E2:E1006), E2:E1006="X"),
+    _xlpm.reviewRows, _xlfn._xlws.FILTER(ROW(E2:E1007), E2:E1007="X"),
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 2531 / 회전초밥</v>
+        <v>Gold / 3190 / 뱀</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -985,19 +989,19 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B19">
-        <v>1021</v>
+        <v>2230</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
@@ -1005,10 +1009,10 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>10431</v>
+        <v>1021</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -1022,10 +1026,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>10866</v>
+        <v>10431</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -1039,10 +1043,10 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>11279</v>
+        <v>10866</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -1056,16 +1060,16 @@
         <v>20</v>
       </c>
       <c r="B23">
-        <v>11286</v>
+        <v>11279</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
@@ -1073,16 +1077,16 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>1138</v>
+        <v>11286</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
@@ -1090,10 +1094,10 @@
         <v>20</v>
       </c>
       <c r="B25">
-        <v>1158</v>
+        <v>1138</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -1107,10 +1111,10 @@
         <v>20</v>
       </c>
       <c r="B26">
-        <v>11723</v>
+        <v>1158</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -1124,10 +1128,10 @@
         <v>20</v>
       </c>
       <c r="B27">
-        <v>11866</v>
+        <v>11723</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -1141,10 +1145,10 @@
         <v>20</v>
       </c>
       <c r="B28">
-        <v>1205</v>
+        <v>11866</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -1158,10 +1162,10 @@
         <v>20</v>
       </c>
       <c r="B29">
-        <v>1244</v>
+        <v>1205</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -1175,10 +1179,10 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>1260</v>
+        <v>1244</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -1192,10 +1196,10 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>13305</v>
+        <v>1260</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -1209,10 +1213,10 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>1406</v>
+        <v>13305</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -1226,10 +1230,10 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>1417</v>
+        <v>1406</v>
       </c>
       <c r="C33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -1243,16 +1247,16 @@
         <v>20</v>
       </c>
       <c r="B34">
-        <v>14940</v>
+        <v>1417</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
@@ -1260,16 +1264,16 @@
         <v>20</v>
       </c>
       <c r="B35">
-        <v>1515</v>
+        <v>14940</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
       </c>
       <c r="E35" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
@@ -1277,10 +1281,10 @@
         <v>20</v>
       </c>
       <c r="B36">
-        <v>1654</v>
+        <v>1515</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -1294,10 +1298,10 @@
         <v>20</v>
       </c>
       <c r="B37">
-        <v>17266</v>
+        <v>1654</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -1311,10 +1315,10 @@
         <v>20</v>
       </c>
       <c r="B38">
-        <v>1927</v>
+        <v>17266</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -1328,10 +1332,10 @@
         <v>20</v>
       </c>
       <c r="B39">
-        <v>1931</v>
+        <v>1927</v>
       </c>
       <c r="C39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -1345,10 +1349,10 @@
         <v>20</v>
       </c>
       <c r="B40">
-        <v>1966</v>
+        <v>1931</v>
       </c>
       <c r="C40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -1362,10 +1366,10 @@
         <v>20</v>
       </c>
       <c r="B41">
-        <v>20006</v>
+        <v>1966</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -1379,10 +1383,10 @@
         <v>20</v>
       </c>
       <c r="B42">
-        <v>2075</v>
+        <v>20006</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -1396,10 +1400,10 @@
         <v>20</v>
       </c>
       <c r="B43">
-        <v>20922</v>
+        <v>2075</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -1413,10 +1417,10 @@
         <v>20</v>
       </c>
       <c r="B44">
-        <v>2164</v>
+        <v>20922</v>
       </c>
       <c r="C44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -1430,10 +1434,10 @@
         <v>20</v>
       </c>
       <c r="B45">
-        <v>2346</v>
+        <v>2164</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -1447,10 +1451,10 @@
         <v>20</v>
       </c>
       <c r="B46">
-        <v>2512</v>
+        <v>2346</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -1464,10 +1468,10 @@
         <v>20</v>
       </c>
       <c r="B47">
-        <v>25757</v>
+        <v>2512</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -1481,10 +1485,10 @@
         <v>20</v>
       </c>
       <c r="B48">
-        <v>2805</v>
+        <v>25757</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -1498,10 +1502,10 @@
         <v>20</v>
       </c>
       <c r="B49">
-        <v>4659</v>
+        <v>2805</v>
       </c>
       <c r="C49" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -1515,10 +1519,10 @@
         <v>20</v>
       </c>
       <c r="B50">
-        <v>5397</v>
+        <v>4659</v>
       </c>
       <c r="C50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -1532,10 +1536,10 @@
         <v>20</v>
       </c>
       <c r="B51">
-        <v>6236</v>
+        <v>5397</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -1549,10 +1553,10 @@
         <v>20</v>
       </c>
       <c r="B52">
-        <v>7568</v>
+        <v>6236</v>
       </c>
       <c r="C52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -1566,10 +1570,10 @@
         <v>20</v>
       </c>
       <c r="B53">
-        <v>8979</v>
+        <v>7568</v>
       </c>
       <c r="C53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -1583,10 +1587,10 @@
         <v>20</v>
       </c>
       <c r="B54">
-        <v>9655</v>
+        <v>8979</v>
       </c>
       <c r="C54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -1600,10 +1604,10 @@
         <v>20</v>
       </c>
       <c r="B55">
-        <v>1541</v>
+        <v>9655</v>
       </c>
       <c r="C55" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -1617,10 +1621,10 @@
         <v>20</v>
       </c>
       <c r="B56">
-        <v>11399</v>
+        <v>1541</v>
       </c>
       <c r="C56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -1634,16 +1638,16 @@
         <v>20</v>
       </c>
       <c r="B57">
-        <v>1789</v>
+        <v>11399</v>
       </c>
       <c r="C57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
       </c>
       <c r="E57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
@@ -1651,10 +1655,10 @@
         <v>20</v>
       </c>
       <c r="B58">
-        <v>11047</v>
+        <v>1789</v>
       </c>
       <c r="C58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -1668,10 +1672,10 @@
         <v>20</v>
       </c>
       <c r="B59">
-        <v>2217</v>
+        <v>11047</v>
       </c>
       <c r="C59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -1685,10 +1689,10 @@
         <v>20</v>
       </c>
       <c r="B60">
-        <v>9017</v>
+        <v>2217</v>
       </c>
       <c r="C60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -1702,10 +1706,10 @@
         <v>20</v>
       </c>
       <c r="B61">
-        <v>1026</v>
+        <v>9017</v>
       </c>
       <c r="C61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -1719,16 +1723,16 @@
         <v>20</v>
       </c>
       <c r="B62">
-        <v>2563</v>
+        <v>1026</v>
       </c>
       <c r="C62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
       </c>
       <c r="E62" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
@@ -1736,10 +1740,10 @@
         <v>20</v>
       </c>
       <c r="B63">
-        <v>21921</v>
+        <v>2563</v>
       </c>
       <c r="C63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -1753,16 +1757,16 @@
         <v>20</v>
       </c>
       <c r="B64">
-        <v>2559</v>
+        <v>21921</v>
       </c>
       <c r="C64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
       </c>
       <c r="E64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.45">
@@ -1770,10 +1774,10 @@
         <v>20</v>
       </c>
       <c r="B65">
-        <v>12847</v>
+        <v>2559</v>
       </c>
       <c r="C65" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -1787,10 +1791,10 @@
         <v>20</v>
       </c>
       <c r="B66">
-        <v>2531</v>
+        <v>12847</v>
       </c>
       <c r="C66" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -1804,15 +1808,32 @@
         <v>20</v>
       </c>
       <c r="B67">
+        <v>2531</v>
+      </c>
+      <c r="C67" t="s">
+        <v>71</v>
+      </c>
+      <c r="D67" t="s">
+        <v>7</v>
+      </c>
+      <c r="E67" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>20</v>
+      </c>
+      <c r="B68">
         <v>10025</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C68" t="s">
         <v>72</v>
       </c>
-      <c r="D67" t="s">
-        <v>7</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+      <c r="E68" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D25AC1-EF9B-4711-A824-D94D34F3D12B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98632D8-CC02-4B3C-999B-2A3211747D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="79">
   <si>
     <t>단계</t>
   </si>
@@ -307,6 +307,10 @@
   </si>
   <si>
     <t>수고르기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수리공항승</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -666,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -695,7 +699,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 3190 / 뱀</v>
+        <v>Silver / 1026 / 보물</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1834,6 +1838,23 @@
         <v>7</v>
       </c>
       <c r="E68" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>20</v>
+      </c>
+      <c r="B69">
+        <v>1449</v>
+      </c>
+      <c r="C69" t="s">
+        <v>78</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+      <c r="E69" t="s">
         <v>8</v>
       </c>
     </row>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98632D8-CC02-4B3C-999B-2A3211747D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62D983E-8D8D-4462-8A35-FDD3E123B7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="80">
   <si>
     <t>단계</t>
   </si>
@@ -311,6 +311,10 @@
   </si>
   <si>
     <t>수리공항승</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주몽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -670,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -699,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1026 / 보물</v>
+        <v>Silver / 11047 / 동전0</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1008,7 +1012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1858,7 +1862,27 @@
         <v>8</v>
       </c>
     </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>20</v>
+      </c>
+      <c r="B70">
+        <v>1940</v>
+      </c>
+      <c r="C70" t="s">
+        <v>79</v>
+      </c>
+      <c r="D70" t="s">
+        <v>7</v>
+      </c>
+      <c r="E70" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:E70">
+    <sortCondition ref="A20:A70"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="G1:H1"/>
   </mergeCells>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62D983E-8D8D-4462-8A35-FDD3E123B7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E02ED6-25A1-4306-8912-582C41C106AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="80">
   <si>
     <t>단계</t>
   </si>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 11047 / 동전0</v>
+        <v>Gold / 1253 / 좋다</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1689,7 +1689,7 @@
         <v>7</v>
       </c>
       <c r="E59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E02ED6-25A1-4306-8912-582C41C106AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9B3861-5F2B-4969-92E0-2A5B75F50251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 1253 / 좋다</v>
+        <v>Gold / 2230 / 수고르기</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -975,7 +975,7 @@
         <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9B3861-5F2B-4969-92E0-2A5B75F50251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B72BDF-9247-47D7-9B13-799020E6C5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 2230 / 수고르기</v>
+        <v>Gold / 15961 / 회전초밥</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1791,7 +1791,7 @@
         <v>7</v>
       </c>
       <c r="E65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B72BDF-9247-47D7-9B13-799020E6C5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA632FFC-8690-4EF3-9379-1906966E65EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 15961 / 회전초밥</v>
+        <v>Gold / 2467 / 용액</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1723,7 +1723,7 @@
         <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA632FFC-8690-4EF3-9379-1906966E65EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A68308-3B9A-419D-8914-5E5AC92E172D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="5200" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOJ 문제 정리" sheetId="1" r:id="rId1"/>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 2467 / 용액</v>
+        <v>Gold / 3190 / 뱀</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1672,7 +1672,7 @@
         <v>7</v>
       </c>
       <c r="E58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A68308-3B9A-419D-8914-5E5AC92E172D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B6CF6C-8985-4327-BC67-6E155DB21D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5200" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 3190 / 뱀</v>
+        <v>Silver / 1026 / 보물</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1009,7 +1009,7 @@
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B6CF6C-8985-4327-BC67-6E155DB21D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018E353E-9F2D-4EE1-96AD-F57A6FCCC458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5200" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1026 / 보물</v>
+        <v>Silver / 2531 / 회전초밥</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1740,7 +1740,7 @@
         <v>7</v>
       </c>
       <c r="E62" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018E353E-9F2D-4EE1-96AD-F57A6FCCC458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BA3221-0D99-40C1-8BB2-D902866247A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5200" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 2531 / 회전초밥</v>
+        <v>Silver / 1449 / 수리공항승</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1825,7 +1825,7 @@
         <v>7</v>
       </c>
       <c r="E67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BA3221-0D99-40C1-8BB2-D902866247A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7729D9-B59A-4726-80B6-BE721105E366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5200" windowWidth="26110" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="5200" windowWidth="25850" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOJ 문제 정리" sheetId="1" r:id="rId1"/>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 1449 / 수리공항승</v>
+        <v>Silver / 14940 / 쉬운최단거리</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1859,7 +1859,7 @@
         <v>7</v>
       </c>
       <c r="E69" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7729D9-B59A-4726-80B6-BE721105E366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9FEDDC-2DB1-4D95-A792-1178891E7996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5200" windowWidth="25850" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 14940 / 쉬운최단거리</v>
+        <v>Gold / 1806 / 부분합</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -924,7 +924,7 @@
         <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9FEDDC-2DB1-4D95-A792-1178891E7996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D78CA3-DE29-4E78-8F0C-44C9588837A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5200" windowWidth="25850" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 1806 / 부분합</v>
+        <v>Gold / 1253 / 좋다</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1842,7 +1842,7 @@
         <v>7</v>
       </c>
       <c r="E68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D78CA3-DE29-4E78-8F0C-44C9588837A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FAEE3B-864A-4D9C-9D10-7842F17B6325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5200" windowWidth="25850" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 1253 / 좋다</v>
+        <v>Gold / 1806 / 부분합</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1706,7 +1706,7 @@
         <v>7</v>
       </c>
       <c r="E60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FAEE3B-864A-4D9C-9D10-7842F17B6325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB31000-6301-4BA2-BFA2-E78C7D04B4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5200" windowWidth="25850" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 1806 / 부분합</v>
+        <v>Gold / 2467 / 용액</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -941,7 +941,7 @@
         <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB31000-6301-4BA2-BFA2-E78C7D04B4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973E5694-FE15-41C8-B3E7-58FFD4B61A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5200" windowWidth="25850" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 2467 / 용액</v>
+        <v>Gold / 1806 / 부분합</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -958,7 +958,7 @@
         <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973E5694-FE15-41C8-B3E7-58FFD4B61A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15A86D6-5505-4470-AB64-02661D61F082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5200" windowWidth="25850" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Gold / 1806 / 부분합</v>
+        <v>Silver / 12847 / 꿀알바</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -907,7 +907,7 @@
         <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15A86D6-5505-4470-AB64-02661D61F082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033ED24B-75ED-4929-81EB-D13D8E3049A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5200" windowWidth="25850" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1876,7 +1876,7 @@
         <v>7</v>
       </c>
       <c r="E70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033ED24B-75ED-4929-81EB-D13D8E3049A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56F69AF-14D4-4FAF-8175-EFA61A634F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5200" windowWidth="25850" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,7 +703,7 @@
     _xlpm.r, INDEX(_xlpm.reviewRows, RANDBETWEEN(1, ROWS(_xlpm.reviewRows))),
     INDEX(A:A,_xlpm.r)&amp;" / "&amp;INDEX(B:B,_xlpm.r)&amp;" / "&amp;INDEX(C:C,_xlpm.r)
 )</f>
-        <v>Silver / 12847 / 꿀알바</v>
+        <v>Gold / 3190 / 뱀</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -1808,7 +1808,7 @@
         <v>7</v>
       </c>
       <c r="E66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56F69AF-14D4-4FAF-8175-EFA61A634F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9B806A-F8B3-402F-A5A6-FF336AFDF22E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5200" windowWidth="25850" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -992,7 +992,7 @@
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">

--- a/BOJ/boj_문제정리.xlsx
+++ b/BOJ/boj_문제정리.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose1\pycharmproject\Study-Coding-Test\BOJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9B806A-F8B3-402F-A5A6-FF336AFDF22E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2232997-D850-4116-B985-97B164D16356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5200" windowWidth="25850" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9930" yWindow="5330" windowWidth="25850" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOJ 문제 정리" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="82">
   <si>
     <t>단계</t>
   </si>
@@ -315,6 +315,14 @@
   </si>
   <si>
     <t>주몽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두수의합</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -674,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1877,6 +1885,23 @@
       </c>
       <c r="E70" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>20</v>
+      </c>
+      <c r="B71">
+        <v>3273</v>
+      </c>
+      <c r="C71" t="s">
+        <v>80</v>
+      </c>
+      <c r="D71" t="s">
+        <v>7</v>
+      </c>
+      <c r="E71" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
